--- a/weeks/week02/data/hand-build-nfl-field-goals-worksheet.xlsx
+++ b/weeks/week02/data/hand-build-nfl-field-goals-worksheet.xlsx
@@ -8,6 +8,8 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="field goals" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="free throws" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="game log" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -16,8 +18,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="0.000"/>
+    <numFmt numFmtId="165" formatCode="0.0000"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -59,7 +62,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -68,12 +71,29 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="1" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
+  <dxfs count="1">
+    <dxf>
+      <font>
+        <color rgb="00006100"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="00C6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
@@ -435,7 +455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q30"/>
+  <dimension ref="A1:T30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -454,6 +474,9 @@
     <col width="13" customWidth="1" min="15" max="15"/>
     <col width="13" customWidth="1" min="16" max="16"/>
     <col width="13" customWidth="1" min="17" max="17"/>
+    <col width="13" customWidth="1" min="18" max="18"/>
+    <col width="13" customWidth="1" min="19" max="19"/>
+    <col width="13" customWidth="1" min="20" max="20"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -529,12 +552,27 @@
       </c>
       <c r="P1" s="2" t="inlineStr">
         <is>
-          <t>Z vs league</t>
+          <t>Z score vs league</t>
         </is>
       </c>
       <c r="Q1" s="2" t="inlineStr">
         <is>
           <t>Interval excludes league rate?</t>
+        </is>
+      </c>
+      <c r="R1" s="2" t="inlineStr">
+        <is>
+          <t>P(next two both made), multiplied</t>
+        </is>
+      </c>
+      <c r="S1" s="2" t="inlineStr">
+        <is>
+          <t>P(next two both made), BINOM.DIST</t>
+        </is>
+      </c>
+      <c r="T1" s="2" t="inlineStr">
+        <is>
+          <t>P(his makes or fewer, at the league rate)</t>
         </is>
       </c>
     </row>
@@ -573,8 +611,11 @@
       <c r="O2" s="5" t="n">
         <v>0.8421999999999999</v>
       </c>
-      <c r="P2" s="6" t="n"/>
+      <c r="P2" s="3" t="n"/>
       <c r="Q2" s="3" t="n"/>
+      <c r="R2" s="4" t="n"/>
+      <c r="S2" s="4" t="n"/>
+      <c r="T2" s="4" t="n"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -1253,13 +1294,1544 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="7" t="inlineStr">
-        <is>
-          <t>Fill in every highlighted cell. Use cell references, not typed-in numbers, so the sheet still works if a row changes.</t>
+      <c r="A30" s="6" t="inlineStr">
+        <is>
+          <t>Fill in every highlighted cell. Each one turns from yellow to green when the answer in it is right, so a sheet with any yellow left in it is not finished. The check allows for rounding, so a value you rounded to three decimals still turns green. Use cell references, not typed-in numbers, so the sheet still works if a row changes. The two P(next two both made) cells ask for the same probability twice, once by multiplying the rate by itself and once with BINOM.DIST. They should agree to every decimal, and if they do not, your BINOM.DIST arguments are in the wrong order.</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="H2">
+    <cfRule type="expression" priority="1" dxfId="0">
+      <formula>AND(ISNUMBER(H2),ABS(H2-(COUNT($D$2:$D$28)))&lt;=MAX(0*ABS(COUNT($D$2:$D$28)),0))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I2">
+    <cfRule type="expression" priority="2" dxfId="0">
+      <formula>AND(ISNUMBER(I2),ABS(I2-(SUM($F$2:$F$28)))&lt;=MAX(0*ABS(SUM($F$2:$F$28)),0))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J2">
+    <cfRule type="expression" priority="3" dxfId="0">
+      <formula>AND(ISNUMBER(J2),ABS(J2-((SUM($F$2:$F$28)/COUNT($D$2:$D$28))))&lt;=MAX(0.02*ABS((SUM($F$2:$F$28)/COUNT($D$2:$D$28))),0.005))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K2">
+    <cfRule type="expression" priority="4" dxfId="0">
+      <formula>AND(ISNUMBER(K2),ABS(K2-(SQRT((SUM($F$2:$F$28)/COUNT($D$2:$D$28))*(1-(SUM($F$2:$F$28)/COUNT($D$2:$D$28)))/COUNT($D$2:$D$28))))&lt;=MAX(0.02*ABS(SQRT((SUM($F$2:$F$28)/COUNT($D$2:$D$28))*(1-(SUM($F$2:$F$28)/COUNT($D$2:$D$28)))/COUNT($D$2:$D$28))),0.005))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L2">
+    <cfRule type="expression" priority="5" dxfId="0">
+      <formula>AND(ISNUMBER(L2),ABS(L2-(1.96*SQRT((SUM($F$2:$F$28)/COUNT($D$2:$D$28))*(1-(SUM($F$2:$F$28)/COUNT($D$2:$D$28)))/COUNT($D$2:$D$28))))&lt;=MAX(0.02*ABS(1.96*SQRT((SUM($F$2:$F$28)/COUNT($D$2:$D$28))*(1-(SUM($F$2:$F$28)/COUNT($D$2:$D$28)))/COUNT($D$2:$D$28))),0.005))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M2">
+    <cfRule type="expression" priority="6" dxfId="0">
+      <formula>AND(ISNUMBER(M2),ABS(M2-((SUM($F$2:$F$28)/COUNT($D$2:$D$28))-(1.96*SQRT((SUM($F$2:$F$28)/COUNT($D$2:$D$28))*(1-(SUM($F$2:$F$28)/COUNT($D$2:$D$28)))/COUNT($D$2:$D$28)))))&lt;=MAX(0.02*ABS((SUM($F$2:$F$28)/COUNT($D$2:$D$28))-(1.96*SQRT((SUM($F$2:$F$28)/COUNT($D$2:$D$28))*(1-(SUM($F$2:$F$28)/COUNT($D$2:$D$28)))/COUNT($D$2:$D$28)))),0.005))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="N2">
+    <cfRule type="expression" priority="7" dxfId="0">
+      <formula>AND(ISNUMBER(N2),ABS(N2-((SUM($F$2:$F$28)/COUNT($D$2:$D$28))+(1.96*SQRT((SUM($F$2:$F$28)/COUNT($D$2:$D$28))*(1-(SUM($F$2:$F$28)/COUNT($D$2:$D$28)))/COUNT($D$2:$D$28)))))&lt;=MAX(0.02*ABS((SUM($F$2:$F$28)/COUNT($D$2:$D$28))+(1.96*SQRT((SUM($F$2:$F$28)/COUNT($D$2:$D$28))*(1-(SUM($F$2:$F$28)/COUNT($D$2:$D$28)))/COUNT($D$2:$D$28)))),0.005))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="P2">
+    <cfRule type="expression" priority="8" dxfId="0">
+      <formula>AND(ISNUMBER(P2),ABS(P2-(((SUM($F$2:$F$28)/COUNT($D$2:$D$28))-$O$2)/(SQRT((SUM($F$2:$F$28)/COUNT($D$2:$D$28))*(1-(SUM($F$2:$F$28)/COUNT($D$2:$D$28)))/COUNT($D$2:$D$28)))))&lt;=MAX(0.02*ABS(((SUM($F$2:$F$28)/COUNT($D$2:$D$28))-$O$2)/(SQRT((SUM($F$2:$F$28)/COUNT($D$2:$D$28))*(1-(SUM($F$2:$F$28)/COUNT($D$2:$D$28)))/COUNT($D$2:$D$28)))),0.05))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Q2">
+    <cfRule type="expression" priority="9" dxfId="0">
+      <formula>AND(Q2&lt;&gt;"",EXACT(LOWER(TRIM(Q2)),LOWER(IF(OR((SUM($F$2:$F$28)/COUNT($D$2:$D$28))+(1.96*SQRT((SUM($F$2:$F$28)/COUNT($D$2:$D$28))*(1-(SUM($F$2:$F$28)/COUNT($D$2:$D$28)))/COUNT($D$2:$D$28)))&lt;$O$2,(SUM($F$2:$F$28)/COUNT($D$2:$D$28))-(1.96*SQRT((SUM($F$2:$F$28)/COUNT($D$2:$D$28))*(1-(SUM($F$2:$F$28)/COUNT($D$2:$D$28)))/COUNT($D$2:$D$28)))&gt;$O$2),"yes","no"))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="R2">
+    <cfRule type="expression" priority="10" dxfId="0">
+      <formula>AND(ISNUMBER(R2),ABS(R2-((SUM($F$2:$F$28)/COUNT($D$2:$D$28))*(SUM($F$2:$F$28)/COUNT($D$2:$D$28))))&lt;=MAX(0.02*ABS((SUM($F$2:$F$28)/COUNT($D$2:$D$28))*(SUM($F$2:$F$28)/COUNT($D$2:$D$28))),0.005))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="S2">
+    <cfRule type="expression" priority="11" dxfId="0">
+      <formula>AND(ISNUMBER(S2),ABS(S2-((SUM($F$2:$F$28)/COUNT($D$2:$D$28))*(SUM($F$2:$F$28)/COUNT($D$2:$D$28))))&lt;=MAX(0.02*ABS((SUM($F$2:$F$28)/COUNT($D$2:$D$28))*(SUM($F$2:$F$28)/COUNT($D$2:$D$28))),0.005))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="T2">
+    <cfRule type="expression" priority="12" dxfId="0">
+      <formula>AND(ISNUMBER(T2),ABS(T2-(_xlfn.BINOM.DIST(SUM($F$2:$F$28),COUNT($D$2:$D$28),$O$2,TRUE)))&lt;=MAX(0.02*ABS(_xlfn.BINOM.DIST(SUM($F$2:$F$28),COUNT($D$2:$D$28),$O$2,TRUE)),0.005))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="34" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Player</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Nick Anderson</t>
+        </is>
+      </c>
+      <c r="D1" s="7" t="inlineStr">
+        <is>
+          <t>Free throw rate</t>
+        </is>
+      </c>
+      <c r="E1" s="8" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>Season</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>1994-95</t>
+        </is>
+      </c>
+      <c r="D2" s="7" t="inlineStr">
+        <is>
+          <t>P(miss on one attempt)</t>
+        </is>
+      </c>
+      <c r="E2" s="8" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>Free throws made</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>143</v>
+      </c>
+      <c r="D3" s="7" t="inlineStr">
+        <is>
+          <t>P(misses all four), rate multiplied</t>
+        </is>
+      </c>
+      <c r="E3" s="8" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Free throws attempted</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>203</v>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>P(misses all four), BINOM.DIST</t>
+        </is>
+      </c>
+      <c r="E4" s="8" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>Attempts in the Finals sequence</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>4</v>
+      </c>
+      <c r="D5" s="7" t="inlineStr">
+        <is>
+          <t>P(makes at least one of the four)</t>
+        </is>
+      </c>
+      <c r="E5" s="8" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>Work the chance he misses all four twice, once by multiplying the miss rate by itself and once with BINOM.DIST, and check that the two agree to every decimal. If they do not, the arguments to BINOM.DIST are in the wrong order. Both routes assume the four attempts are independent of each other and that his season rate is the right rate for those four attempts. Be ready to say in class which of those two assumptions you trust less.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="E1">
+    <cfRule type="expression" priority="1" dxfId="0">
+      <formula>AND(ISNUMBER(E1),ABS(E1-(($B$3/$B$4)))&lt;=MAX(0.02*ABS(($B$3/$B$4)),0.002))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E2">
+    <cfRule type="expression" priority="2" dxfId="0">
+      <formula>AND(ISNUMBER(E2),ABS(E2-((1-($B$3/$B$4))))&lt;=MAX(0.02*ABS((1-($B$3/$B$4))),0.002))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E3">
+    <cfRule type="expression" priority="3" dxfId="0">
+      <formula>AND(ISNUMBER(E3),ABS(E3-((1-($B$3/$B$4))^$B$5))&lt;=MAX(0.02*ABS((1-($B$3/$B$4))^$B$5),0.0002))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E4">
+    <cfRule type="expression" priority="4" dxfId="0">
+      <formula>AND(ISNUMBER(E4),ABS(E4-((1-($B$3/$B$4))^$B$5))&lt;=MAX(0.02*ABS((1-($B$3/$B$4))^$B$5),0.0002))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E5">
+    <cfRule type="expression" priority="5" dxfId="0">
+      <formula>AND(ISNUMBER(E5),ABS(E5-((1-(1-($B$3/$B$4))^$B$5)))&lt;=MAX(0.02*ABS((1-(1-($B$3/$B$4))^$B$5)),0.002))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I79"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="7" customWidth="1" min="1" max="1"/>
+    <col width="7" customWidth="1" min="2" max="2"/>
+    <col width="7" customWidth="1" min="3" max="3"/>
+    <col width="7" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Game</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>PTS</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>TRB</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>AST</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Statistic</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Points</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Rebounds</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Assists</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="n">
+        <v>30</v>
+      </c>
+      <c r="C2" t="n">
+        <v>7</v>
+      </c>
+      <c r="D2" t="n">
+        <v>3</v>
+      </c>
+      <c r="F2" s="7" t="inlineStr">
+        <is>
+          <t>Games</t>
+        </is>
+      </c>
+      <c r="G2" s="9" t="n"/>
+      <c r="H2" s="9" t="n"/>
+      <c r="I2" s="9" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="n">
+        <v>30</v>
+      </c>
+      <c r="C3" t="n">
+        <v>8</v>
+      </c>
+      <c r="D3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F3" s="7" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="n"/>
+      <c r="H3" s="4" t="n"/>
+      <c r="I3" s="4" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="n">
+        <v>28</v>
+      </c>
+      <c r="C4" t="n">
+        <v>4</v>
+      </c>
+      <c r="D4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>Standard deviation</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="n"/>
+      <c r="H4" s="4" t="n"/>
+      <c r="I4" s="4" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="n">
+        <v>16</v>
+      </c>
+      <c r="C5" t="n">
+        <v>6</v>
+      </c>
+      <c r="D5" t="n">
+        <v>2</v>
+      </c>
+      <c r="F5" s="7" t="inlineStr">
+        <is>
+          <t>Standard error</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="n"/>
+      <c r="H5" s="4" t="n"/>
+      <c r="I5" s="4" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="n">
+        <v>28</v>
+      </c>
+      <c r="C6" t="n">
+        <v>11</v>
+      </c>
+      <c r="D6" t="n">
+        <v>2</v>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>Relative spread</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="n"/>
+      <c r="H6" s="4" t="n"/>
+      <c r="I6" s="4" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="n">
+        <v>34</v>
+      </c>
+      <c r="C7" t="n">
+        <v>6</v>
+      </c>
+      <c r="D7" t="n">
+        <v>3</v>
+      </c>
+      <c r="F7" s="7" t="inlineStr">
+        <is>
+          <t>95% interval low</t>
+        </is>
+      </c>
+      <c r="G7" s="4" t="n"/>
+      <c r="H7" s="4" t="n"/>
+      <c r="I7" s="4" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="n">
+        <v>31</v>
+      </c>
+      <c r="C8" t="n">
+        <v>7</v>
+      </c>
+      <c r="D8" t="n">
+        <v>2</v>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>95% interval high</t>
+        </is>
+      </c>
+      <c r="G8" s="4" t="n"/>
+      <c r="H8" s="4" t="n"/>
+      <c r="I8" s="4" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="n">
+        <v>34</v>
+      </c>
+      <c r="C9" t="n">
+        <v>4</v>
+      </c>
+      <c r="D9" t="n">
+        <v>3</v>
+      </c>
+      <c r="F9" s="7" t="inlineStr">
+        <is>
+          <t>Standard errors between his average and 30 points a game</t>
+        </is>
+      </c>
+      <c r="G9" s="10" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="n">
+        <v>23</v>
+      </c>
+      <c r="C10" t="n">
+        <v>7</v>
+      </c>
+      <c r="D10" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="n">
+        <v>30</v>
+      </c>
+      <c r="C11" t="n">
+        <v>6</v>
+      </c>
+      <c r="D11" t="n">
+        <v>4</v>
+      </c>
+      <c r="F11" s="6" t="inlineStr">
+        <is>
+          <t>Relative spread is the standard deviation divided by the average, which is the coefficient of variation from Week 1. It puts three statistics on three different scales in one column. The same 78 games produced all three columns, so anything that differs between them is the spread of the statistic and nothing else. Use COUNT, AVERAGE, STDEV.S and SQRT, and build every cell from cell references.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="n">
+        <v>24</v>
+      </c>
+      <c r="C12" t="n">
+        <v>4</v>
+      </c>
+      <c r="D12" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="n">
+        <v>28</v>
+      </c>
+      <c r="C13" t="n">
+        <v>8</v>
+      </c>
+      <c r="D13" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="n">
+        <v>32</v>
+      </c>
+      <c r="C14" t="n">
+        <v>11</v>
+      </c>
+      <c r="D14" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="n">
+        <v>25</v>
+      </c>
+      <c r="C15" t="n">
+        <v>8</v>
+      </c>
+      <c r="D15" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" t="n">
+        <v>18</v>
+      </c>
+      <c r="C16" t="n">
+        <v>2</v>
+      </c>
+      <c r="D16" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" t="n">
+        <v>26</v>
+      </c>
+      <c r="C17" t="n">
+        <v>11</v>
+      </c>
+      <c r="D17" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="n">
+        <v>28</v>
+      </c>
+      <c r="C18" t="n">
+        <v>7</v>
+      </c>
+      <c r="D18" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="n">
+        <v>29</v>
+      </c>
+      <c r="C19" t="n">
+        <v>5</v>
+      </c>
+      <c r="D19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" t="n">
+        <v>30</v>
+      </c>
+      <c r="C20" t="n">
+        <v>11</v>
+      </c>
+      <c r="D20" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" t="n">
+        <v>25</v>
+      </c>
+      <c r="C21" t="n">
+        <v>5</v>
+      </c>
+      <c r="D21" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" t="n">
+        <v>25</v>
+      </c>
+      <c r="C22" t="n">
+        <v>7</v>
+      </c>
+      <c r="D22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" t="n">
+        <v>32</v>
+      </c>
+      <c r="C23" t="n">
+        <v>7</v>
+      </c>
+      <c r="D23" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" t="n">
+        <v>24</v>
+      </c>
+      <c r="C24" t="n">
+        <v>2</v>
+      </c>
+      <c r="D24" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" t="n">
+        <v>28</v>
+      </c>
+      <c r="C25" t="n">
+        <v>4</v>
+      </c>
+      <c r="D25" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" t="n">
+        <v>32</v>
+      </c>
+      <c r="C26" t="n">
+        <v>7</v>
+      </c>
+      <c r="D26" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" t="n">
+        <v>26</v>
+      </c>
+      <c r="C27" t="n">
+        <v>7</v>
+      </c>
+      <c r="D27" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" t="n">
+        <v>44</v>
+      </c>
+      <c r="C28" t="n">
+        <v>7</v>
+      </c>
+      <c r="D28" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" t="n">
+        <v>28</v>
+      </c>
+      <c r="C29" t="n">
+        <v>5</v>
+      </c>
+      <c r="D29" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" t="n">
+        <v>27</v>
+      </c>
+      <c r="C30" t="n">
+        <v>2</v>
+      </c>
+      <c r="D30" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" t="n">
+        <v>33</v>
+      </c>
+      <c r="C31" t="n">
+        <v>4</v>
+      </c>
+      <c r="D31" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" t="n">
+        <v>16</v>
+      </c>
+      <c r="C32" t="n">
+        <v>4</v>
+      </c>
+      <c r="D32" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" t="n">
+        <v>28</v>
+      </c>
+      <c r="C33" t="n">
+        <v>9</v>
+      </c>
+      <c r="D33" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" t="n">
+        <v>28</v>
+      </c>
+      <c r="C34" t="n">
+        <v>2</v>
+      </c>
+      <c r="D34" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" t="n">
+        <v>40</v>
+      </c>
+      <c r="C35" t="n">
+        <v>8</v>
+      </c>
+      <c r="D35" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" t="n">
+        <v>30</v>
+      </c>
+      <c r="C36" t="n">
+        <v>6</v>
+      </c>
+      <c r="D36" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" t="n">
+        <v>36</v>
+      </c>
+      <c r="C37" t="n">
+        <v>4</v>
+      </c>
+      <c r="D37" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" t="n">
+        <v>24</v>
+      </c>
+      <c r="C38" t="n">
+        <v>8</v>
+      </c>
+      <c r="D38" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" t="n">
+        <v>22</v>
+      </c>
+      <c r="C39" t="n">
+        <v>4</v>
+      </c>
+      <c r="D39" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" t="n">
+        <v>30</v>
+      </c>
+      <c r="C40" t="n">
+        <v>12</v>
+      </c>
+      <c r="D40" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" t="n">
+        <v>22</v>
+      </c>
+      <c r="C41" t="n">
+        <v>8</v>
+      </c>
+      <c r="D41" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" t="n">
+        <v>47</v>
+      </c>
+      <c r="C42" t="n">
+        <v>18</v>
+      </c>
+      <c r="D42" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" t="n">
+        <v>40</v>
+      </c>
+      <c r="C43" t="n">
+        <v>7</v>
+      </c>
+      <c r="D43" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" t="n">
+        <v>33</v>
+      </c>
+      <c r="C44" t="n">
+        <v>10</v>
+      </c>
+      <c r="D44" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>44</v>
+      </c>
+      <c r="B45" t="n">
+        <v>43</v>
+      </c>
+      <c r="C45" t="n">
+        <v>10</v>
+      </c>
+      <c r="D45" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>45</v>
+      </c>
+      <c r="B46" t="n">
+        <v>24</v>
+      </c>
+      <c r="C46" t="n">
+        <v>11</v>
+      </c>
+      <c r="D46" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>46</v>
+      </c>
+      <c r="B47" t="n">
+        <v>21</v>
+      </c>
+      <c r="C47" t="n">
+        <v>12</v>
+      </c>
+      <c r="D47" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>47</v>
+      </c>
+      <c r="B48" t="n">
+        <v>31</v>
+      </c>
+      <c r="C48" t="n">
+        <v>10</v>
+      </c>
+      <c r="D48" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>48</v>
+      </c>
+      <c r="B49" t="n">
+        <v>35</v>
+      </c>
+      <c r="C49" t="n">
+        <v>6</v>
+      </c>
+      <c r="D49" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>49</v>
+      </c>
+      <c r="B50" t="n">
+        <v>29</v>
+      </c>
+      <c r="C50" t="n">
+        <v>5</v>
+      </c>
+      <c r="D50" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>50</v>
+      </c>
+      <c r="B51" t="n">
+        <v>17</v>
+      </c>
+      <c r="C51" t="n">
+        <v>7</v>
+      </c>
+      <c r="D51" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>51</v>
+      </c>
+      <c r="B52" t="n">
+        <v>21</v>
+      </c>
+      <c r="C52" t="n">
+        <v>8</v>
+      </c>
+      <c r="D52" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>52</v>
+      </c>
+      <c r="B53" t="n">
+        <v>30</v>
+      </c>
+      <c r="C53" t="n">
+        <v>9</v>
+      </c>
+      <c r="D53" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>53</v>
+      </c>
+      <c r="B54" t="n">
+        <v>23</v>
+      </c>
+      <c r="C54" t="n">
+        <v>16</v>
+      </c>
+      <c r="D54" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>54</v>
+      </c>
+      <c r="B55" t="n">
+        <v>21</v>
+      </c>
+      <c r="C55" t="n">
+        <v>4</v>
+      </c>
+      <c r="D55" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>55</v>
+      </c>
+      <c r="B56" t="n">
+        <v>21</v>
+      </c>
+      <c r="C56" t="n">
+        <v>3</v>
+      </c>
+      <c r="D56" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>56</v>
+      </c>
+      <c r="B57" t="n">
+        <v>29</v>
+      </c>
+      <c r="C57" t="n">
+        <v>8</v>
+      </c>
+      <c r="D57" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>57</v>
+      </c>
+      <c r="B58" t="n">
+        <v>18</v>
+      </c>
+      <c r="C58" t="n">
+        <v>8</v>
+      </c>
+      <c r="D58" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>58</v>
+      </c>
+      <c r="B59" t="n">
+        <v>23</v>
+      </c>
+      <c r="C59" t="n">
+        <v>6</v>
+      </c>
+      <c r="D59" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>59</v>
+      </c>
+      <c r="B60" t="n">
+        <v>34</v>
+      </c>
+      <c r="C60" t="n">
+        <v>16</v>
+      </c>
+      <c r="D60" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>60</v>
+      </c>
+      <c r="B61" t="n">
+        <v>24</v>
+      </c>
+      <c r="C61" t="n">
+        <v>9</v>
+      </c>
+      <c r="D61" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>61</v>
+      </c>
+      <c r="B62" t="n">
+        <v>19</v>
+      </c>
+      <c r="C62" t="n">
+        <v>3</v>
+      </c>
+      <c r="D62" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>62</v>
+      </c>
+      <c r="B63" t="n">
+        <v>32</v>
+      </c>
+      <c r="C63" t="n">
+        <v>3</v>
+      </c>
+      <c r="D63" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>63</v>
+      </c>
+      <c r="B64" t="n">
+        <v>29</v>
+      </c>
+      <c r="C64" t="n">
+        <v>7</v>
+      </c>
+      <c r="D64" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>64</v>
+      </c>
+      <c r="B65" t="n">
+        <v>25</v>
+      </c>
+      <c r="C65" t="n">
+        <v>2</v>
+      </c>
+      <c r="D65" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>65</v>
+      </c>
+      <c r="B66" t="n">
+        <v>20</v>
+      </c>
+      <c r="C66" t="n">
+        <v>5</v>
+      </c>
+      <c r="D66" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>66</v>
+      </c>
+      <c r="B67" t="n">
+        <v>29</v>
+      </c>
+      <c r="C67" t="n">
+        <v>2</v>
+      </c>
+      <c r="D67" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>67</v>
+      </c>
+      <c r="B68" t="n">
+        <v>23</v>
+      </c>
+      <c r="C68" t="n">
+        <v>2</v>
+      </c>
+      <c r="D68" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>68</v>
+      </c>
+      <c r="B69" t="n">
+        <v>21</v>
+      </c>
+      <c r="C69" t="n">
+        <v>3</v>
+      </c>
+      <c r="D69" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>69</v>
+      </c>
+      <c r="B70" t="n">
+        <v>39</v>
+      </c>
+      <c r="C70" t="n">
+        <v>6</v>
+      </c>
+      <c r="D70" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>70</v>
+      </c>
+      <c r="B71" t="n">
+        <v>22</v>
+      </c>
+      <c r="C71" t="n">
+        <v>4</v>
+      </c>
+      <c r="D71" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>71</v>
+      </c>
+      <c r="B72" t="n">
+        <v>25</v>
+      </c>
+      <c r="C72" t="n">
+        <v>11</v>
+      </c>
+      <c r="D72" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>72</v>
+      </c>
+      <c r="B73" t="n">
+        <v>23</v>
+      </c>
+      <c r="C73" t="n">
+        <v>6</v>
+      </c>
+      <c r="D73" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>73</v>
+      </c>
+      <c r="B74" t="n">
+        <v>32</v>
+      </c>
+      <c r="C74" t="n">
+        <v>9</v>
+      </c>
+      <c r="D74" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>74</v>
+      </c>
+      <c r="B75" t="n">
+        <v>29</v>
+      </c>
+      <c r="C75" t="n">
+        <v>7</v>
+      </c>
+      <c r="D75" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>75</v>
+      </c>
+      <c r="B76" t="n">
+        <v>28</v>
+      </c>
+      <c r="C76" t="n">
+        <v>7</v>
+      </c>
+      <c r="D76" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>76</v>
+      </c>
+      <c r="B77" t="n">
+        <v>31</v>
+      </c>
+      <c r="C77" t="n">
+        <v>4</v>
+      </c>
+      <c r="D77" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>77</v>
+      </c>
+      <c r="B78" t="n">
+        <v>32</v>
+      </c>
+      <c r="C78" t="n">
+        <v>8</v>
+      </c>
+      <c r="D78" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>78</v>
+      </c>
+      <c r="B79" t="n">
+        <v>14</v>
+      </c>
+      <c r="C79" t="n">
+        <v>6</v>
+      </c>
+      <c r="D79" t="n">
+        <v>2</v>
+      </c>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="G2">
+    <cfRule type="expression" priority="1" dxfId="0">
+      <formula>AND(ISNUMBER(G2),ABS(G2-(COUNT($B$2:$B$79)))&lt;=MAX(0*ABS(COUNT($B$2:$B$79)),0))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G3">
+    <cfRule type="expression" priority="2" dxfId="0">
+      <formula>AND(ISNUMBER(G3),ABS(G3-(AVERAGE($B$2:$B$79)))&lt;=MAX(0.02*ABS(AVERAGE($B$2:$B$79)),0.005))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G4">
+    <cfRule type="expression" priority="3" dxfId="0">
+      <formula>AND(ISNUMBER(G4),ABS(G4-(_xlfn.STDEV.S($B$2:$B$79)))&lt;=MAX(0.02*ABS(_xlfn.STDEV.S($B$2:$B$79)),0.005))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G5">
+    <cfRule type="expression" priority="4" dxfId="0">
+      <formula>AND(ISNUMBER(G5),ABS(G5-((_xlfn.STDEV.S($B$2:$B$79)/SQRT(COUNT($B$2:$B$79)))))&lt;=MAX(0.02*ABS((_xlfn.STDEV.S($B$2:$B$79)/SQRT(COUNT($B$2:$B$79)))),0.005))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G6">
+    <cfRule type="expression" priority="5" dxfId="0">
+      <formula>AND(ISNUMBER(G6),ABS(G6-((_xlfn.STDEV.S($B$2:$B$79)/AVERAGE($B$2:$B$79))))&lt;=MAX(0.02*ABS((_xlfn.STDEV.S($B$2:$B$79)/AVERAGE($B$2:$B$79))),0.005))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G7">
+    <cfRule type="expression" priority="6" dxfId="0">
+      <formula>AND(ISNUMBER(G7),ABS(G7-((AVERAGE($B$2:$B$79)-1.96*(_xlfn.STDEV.S($B$2:$B$79)/SQRT(COUNT($B$2:$B$79))))))&lt;=MAX(0.02*ABS((AVERAGE($B$2:$B$79)-1.96*(_xlfn.STDEV.S($B$2:$B$79)/SQRT(COUNT($B$2:$B$79))))),0.005))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G8">
+    <cfRule type="expression" priority="7" dxfId="0">
+      <formula>AND(ISNUMBER(G8),ABS(G8-((AVERAGE($B$2:$B$79)+1.96*(_xlfn.STDEV.S($B$2:$B$79)/SQRT(COUNT($B$2:$B$79))))))&lt;=MAX(0.02*ABS((AVERAGE($B$2:$B$79)+1.96*(_xlfn.STDEV.S($B$2:$B$79)/SQRT(COUNT($B$2:$B$79))))),0.005))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H2">
+    <cfRule type="expression" priority="8" dxfId="0">
+      <formula>AND(ISNUMBER(H2),ABS(H2-(COUNT($C$2:$C$79)))&lt;=MAX(0*ABS(COUNT($C$2:$C$79)),0))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H3">
+    <cfRule type="expression" priority="9" dxfId="0">
+      <formula>AND(ISNUMBER(H3),ABS(H3-(AVERAGE($C$2:$C$79)))&lt;=MAX(0.02*ABS(AVERAGE($C$2:$C$79)),0.005))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H4">
+    <cfRule type="expression" priority="10" dxfId="0">
+      <formula>AND(ISNUMBER(H4),ABS(H4-(_xlfn.STDEV.S($C$2:$C$79)))&lt;=MAX(0.02*ABS(_xlfn.STDEV.S($C$2:$C$79)),0.005))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H5">
+    <cfRule type="expression" priority="11" dxfId="0">
+      <formula>AND(ISNUMBER(H5),ABS(H5-((_xlfn.STDEV.S($C$2:$C$79)/SQRT(COUNT($C$2:$C$79)))))&lt;=MAX(0.02*ABS((_xlfn.STDEV.S($C$2:$C$79)/SQRT(COUNT($C$2:$C$79)))),0.005))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H6">
+    <cfRule type="expression" priority="12" dxfId="0">
+      <formula>AND(ISNUMBER(H6),ABS(H6-((_xlfn.STDEV.S($C$2:$C$79)/AVERAGE($C$2:$C$79))))&lt;=MAX(0.02*ABS((_xlfn.STDEV.S($C$2:$C$79)/AVERAGE($C$2:$C$79))),0.005))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H7">
+    <cfRule type="expression" priority="13" dxfId="0">
+      <formula>AND(ISNUMBER(H7),ABS(H7-((AVERAGE($C$2:$C$79)-1.96*(_xlfn.STDEV.S($C$2:$C$79)/SQRT(COUNT($C$2:$C$79))))))&lt;=MAX(0.02*ABS((AVERAGE($C$2:$C$79)-1.96*(_xlfn.STDEV.S($C$2:$C$79)/SQRT(COUNT($C$2:$C$79))))),0.005))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H8">
+    <cfRule type="expression" priority="14" dxfId="0">
+      <formula>AND(ISNUMBER(H8),ABS(H8-((AVERAGE($C$2:$C$79)+1.96*(_xlfn.STDEV.S($C$2:$C$79)/SQRT(COUNT($C$2:$C$79))))))&lt;=MAX(0.02*ABS((AVERAGE($C$2:$C$79)+1.96*(_xlfn.STDEV.S($C$2:$C$79)/SQRT(COUNT($C$2:$C$79))))),0.005))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I2">
+    <cfRule type="expression" priority="15" dxfId="0">
+      <formula>AND(ISNUMBER(I2),ABS(I2-(COUNT($D$2:$D$79)))&lt;=MAX(0*ABS(COUNT($D$2:$D$79)),0))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I3">
+    <cfRule type="expression" priority="16" dxfId="0">
+      <formula>AND(ISNUMBER(I3),ABS(I3-(AVERAGE($D$2:$D$79)))&lt;=MAX(0.02*ABS(AVERAGE($D$2:$D$79)),0.005))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I4">
+    <cfRule type="expression" priority="17" dxfId="0">
+      <formula>AND(ISNUMBER(I4),ABS(I4-(_xlfn.STDEV.S($D$2:$D$79)))&lt;=MAX(0.02*ABS(_xlfn.STDEV.S($D$2:$D$79)),0.005))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I5">
+    <cfRule type="expression" priority="18" dxfId="0">
+      <formula>AND(ISNUMBER(I5),ABS(I5-((_xlfn.STDEV.S($D$2:$D$79)/SQRT(COUNT($D$2:$D$79)))))&lt;=MAX(0.02*ABS((_xlfn.STDEV.S($D$2:$D$79)/SQRT(COUNT($D$2:$D$79)))),0.005))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I6">
+    <cfRule type="expression" priority="19" dxfId="0">
+      <formula>AND(ISNUMBER(I6),ABS(I6-((_xlfn.STDEV.S($D$2:$D$79)/AVERAGE($D$2:$D$79))))&lt;=MAX(0.02*ABS((_xlfn.STDEV.S($D$2:$D$79)/AVERAGE($D$2:$D$79))),0.005))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I7">
+    <cfRule type="expression" priority="20" dxfId="0">
+      <formula>AND(ISNUMBER(I7),ABS(I7-((AVERAGE($D$2:$D$79)-1.96*(_xlfn.STDEV.S($D$2:$D$79)/SQRT(COUNT($D$2:$D$79))))))&lt;=MAX(0.02*ABS((AVERAGE($D$2:$D$79)-1.96*(_xlfn.STDEV.S($D$2:$D$79)/SQRT(COUNT($D$2:$D$79))))),0.005))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I8">
+    <cfRule type="expression" priority="21" dxfId="0">
+      <formula>AND(ISNUMBER(I8),ABS(I8-((AVERAGE($D$2:$D$79)+1.96*(_xlfn.STDEV.S($D$2:$D$79)/SQRT(COUNT($D$2:$D$79))))))&lt;=MAX(0.02*ABS((AVERAGE($D$2:$D$79)+1.96*(_xlfn.STDEV.S($D$2:$D$79)/SQRT(COUNT($D$2:$D$79))))),0.005))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G9">
+    <cfRule type="expression" priority="22" dxfId="0">
+      <formula>AND(ISNUMBER(G9),ABS(G9-(((30-AVERAGE($B$2:$B$79))/(_xlfn.STDEV.S($B$2:$B$79)/SQRT(COUNT($B$2:$B$79))))))&lt;=MAX(0.02*ABS(((30-AVERAGE($B$2:$B$79))/(_xlfn.STDEV.S($B$2:$B$79)/SQRT(COUNT($B$2:$B$79))))),0.05))</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>